--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Library/CloudStorage/OneDrive-UniversidadPolitécnicadeMadrid/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C182B15-46F2-7E49-A016-90E34FC2321D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D241B760-3793-FA49-A5F7-9002FC87F6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7700" yWindow="1800" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AF$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AF$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="155">
   <si>
     <t>Año</t>
   </si>
@@ -483,15 +483,28 @@
   </si>
   <si>
     <t>Specialization: FullStack Web Development</t>
+  </si>
+  <si>
+    <t>Hackathon IndesiaHack 2026</t>
+  </si>
+  <si>
+    <t>Hackathon HackSpain</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -666,69 +679,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -739,39 +756,39 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1077,10 +1094,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF48"/>
+  <dimension ref="A1:AF50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="15" customWidth="1"/>
@@ -1165,7 +1182,7 @@
       <c r="AE1" s="9"/>
       <c r="AF1" s="9"/>
     </row>
-    <row r="2" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
@@ -1189,7 +1206,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>16</v>
       </c>
@@ -1213,7 +1230,7 @@
       <c r="K3" s="9"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -1237,7 +1254,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:32" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>16</v>
       </c>
@@ -1257,7 +1274,7 @@
       </c>
       <c r="J5" s="22"/>
     </row>
-    <row r="6" spans="1:32" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
@@ -1277,7 +1294,7 @@
       </c>
       <c r="J6" s="22"/>
     </row>
-    <row r="7" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
@@ -1297,7 +1314,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="8" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>16</v>
       </c>
@@ -1317,7 +1334,7 @@
       </c>
       <c r="J8" s="22"/>
     </row>
-    <row r="9" spans="1:32" s="20" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" s="20" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>16</v>
       </c>
@@ -1358,7 +1375,7 @@
       <c r="AB9" s="17"/>
       <c r="AC9" s="17"/>
     </row>
-    <row r="10" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>16</v>
       </c>
@@ -1378,7 +1395,7 @@
       </c>
       <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:32" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
@@ -1398,7 +1415,7 @@
       </c>
       <c r="J11" s="37"/>
     </row>
-    <row r="12" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>16</v>
       </c>
@@ -1418,7 +1435,7 @@
       </c>
       <c r="J12" s="37"/>
     </row>
-    <row r="13" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -1438,7 +1455,7 @@
       </c>
       <c r="J13" s="22"/>
     </row>
-    <row r="14" spans="1:32" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>16</v>
       </c>
@@ -1460,7 +1477,7 @@
       </c>
       <c r="J14" s="22"/>
     </row>
-    <row r="15" spans="1:32" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
@@ -1672,7 +1689,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>15</v>
       </c>
@@ -1696,7 +1713,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>15</v>
       </c>
@@ -1720,7 +1737,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>15</v>
       </c>
@@ -1744,7 +1761,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>15</v>
       </c>
@@ -1816,7 +1833,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>15</v>
       </c>
@@ -1841,7 +1858,7 @@
       </c>
       <c r="K29" s="24"/>
     </row>
-    <row r="30" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>15</v>
       </c>
@@ -1866,7 +1883,7 @@
       </c>
       <c r="K30" s="24"/>
     </row>
-    <row r="31" spans="1:29" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>15</v>
       </c>
@@ -1891,7 +1908,7 @@
       </c>
       <c r="K31" s="24"/>
     </row>
-    <row r="32" spans="1:29" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>15</v>
       </c>
@@ -1915,7 +1932,7 @@
       </c>
       <c r="K32" s="24"/>
     </row>
-    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>15</v>
       </c>
@@ -1940,7 +1957,7 @@
       </c>
       <c r="K33" s="24"/>
     </row>
-    <row r="34" spans="1:11" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>15</v>
       </c>
@@ -1990,7 +2007,7 @@
       </c>
       <c r="K35" s="24"/>
     </row>
-    <row r="36" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>115</v>
       </c>
@@ -2013,7 +2030,7 @@
       <c r="J36" s="39"/>
       <c r="K36" s="24"/>
     </row>
-    <row r="37" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="25" t="s">
         <v>115</v>
       </c>
@@ -2033,7 +2050,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>115</v>
       </c>
@@ -2054,258 +2071,287 @@
       </c>
       <c r="J38" s="22"/>
     </row>
-    <row r="39" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="25" t="s">
+    <row r="39" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>121</v>
+      <c r="B39" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>153</v>
       </c>
       <c r="E39" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F39" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="26" t="s">
+      <c r="I39" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="J39" s="39"/>
-    </row>
-    <row r="40" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J39" s="22"/>
+    </row>
+    <row r="40" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="s">
         <v>115</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>86</v>
+        <v>20</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" s="10">
+        <v>2025</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J40" s="39"/>
     </row>
-    <row r="41" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="27" t="s">
+    <row r="41" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="B41" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>126</v>
+      <c r="B41" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>154</v>
       </c>
       <c r="E41" s="10">
         <v>2026</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="J41" s="22"/>
+      <c r="J41" s="39"/>
     </row>
     <row r="42" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="29" t="s">
+      <c r="A42" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="J42" s="39"/>
+    </row>
+    <row r="43" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J43" s="22"/>
+    </row>
+    <row r="44" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C44" s="29" t="s">
         <v>128</v>
-      </c>
-      <c r="E42" s="10">
-        <v>2026</v>
-      </c>
-      <c r="F42" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="11">
-        <v>2026</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J43" s="22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="31" t="s">
-        <v>133</v>
       </c>
       <c r="E44" s="10">
         <v>2026</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="H44" s="7" t="s">
+      <c r="F44" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44" s="30" t="s">
         <v>90</v>
       </c>
       <c r="I44" s="7"/>
-      <c r="J44" s="38" t="s">
+      <c r="J44" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="K44" s="24"/>
-    </row>
-    <row r="45" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="10">
+    </row>
+    <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="7"/>
+      <c r="E45" s="11">
         <v>2026</v>
       </c>
-      <c r="F45" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="H45" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="I45" s="7"/>
+      <c r="F45" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="J45" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" t="s">
-        <v>136</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>133</v>
       </c>
       <c r="E46" s="10">
         <v>2026</v>
       </c>
-      <c r="F46" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="G46" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="H46" s="34" t="s">
+      <c r="F46" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="J46" s="40" t="s">
+      <c r="I46" s="7"/>
+      <c r="J46" s="38" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>141</v>
+      <c r="K46" s="24"/>
+    </row>
+    <row r="47" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>135</v>
       </c>
       <c r="E47" s="10">
         <v>2026</v>
       </c>
-      <c r="F47" s="34" t="s">
+      <c r="F47" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H47" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A48" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J48" s="40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F49" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="G47" s="34" t="s">
+      <c r="G49" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H47" s="34" t="s">
+      <c r="H49" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="J47" s="41" t="s">
+      <c r="J49" s="41" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="11" t="s">
+    <row r="50" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D48" s="7"/>
-      <c r="E48" s="11" t="s">
+      <c r="D50" s="7"/>
+      <c r="E50" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F50" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G50" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H48" s="42" t="s">
+      <c r="H50" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="J48" s="22" t="s">
+      <c r="J50" s="22" t="s">
         <v>148</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF48" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Course"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Madrid Council"/>
-        <filter val="Ministry for Digital Transformation and Public Administration (Government of Spain)"/>
-        <filter val="UPM"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Library/CloudStorage/OneDrive-UniversidadPolitécnicadeMadrid/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D241B760-3793-FA49-A5F7-9002FC87F6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA83FDDF-4B08-AC4C-9075-2EA07C7DB41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7700" yWindow="1800" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="160">
   <si>
     <t>Año</t>
   </si>
@@ -489,15 +489,45 @@
   </si>
   <si>
     <t>Hackathon HackSpain</t>
+  </si>
+  <si>
+    <t>IA para el personal técnico y de gestión de la investigación. XI Encuentro de personal técnico y de gestión de internacionalización del CSIC</t>
+  </si>
+  <si>
+    <t>AI for technical and research management staff. 11th Meeting of technical and internationalization management staff at CSIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+UPM por la ELA: Ingeniería e Innovación para cambiar vidas</t>
+  </si>
+  <si>
+    <t>UPM for ALS: Engineering and Innovation to Change Lives</t>
+  </si>
+  <si>
+    <t>Technology and Health</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -679,112 +709,120 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1097,7 +1135,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF50"/>
+  <dimension ref="A1:AF52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="15" customWidth="1"/>
@@ -2350,6 +2388,52 @@
         <v>148</v>
       </c>
     </row>
+    <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A51" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F51" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A52" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="E52" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F52" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="49" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AF1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
